--- a/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-4B-Instruct-2507/aae/total_votes_file.xlsx
+++ b/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-4B-Instruct-2507/aae/total_votes_file.xlsx
@@ -430,7 +430,7 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D2">
         <v>743</v>
@@ -439,7 +439,7 @@
         <v>3</v>
       </c>
       <c r="G2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H2">
         <v>852</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D3">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H3">
         <v>852</v>
